--- a/Requisitos Fun e NFun.xlsx
+++ b/Requisitos Fun e NFun.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
   <si>
     <t>Código</t>
   </si>
@@ -357,32 +357,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">O sistema deve apresentar uma </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>interface de listagem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> que exiba todos os eventos cadastrados </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">O sistema deve permitir a </t>
     </r>
     <r>
@@ -443,9 +417,6 @@
     <t>O sistema deve permitir a edição de informações de eventos já cadastrados através de um botão "Gerenciar Eventos".</t>
   </si>
   <si>
-    <t>O sistema deve listar automaticamente na tela inicial todos os eventos cadastrados</t>
-  </si>
-  <si>
     <t>RF31</t>
   </si>
   <si>
@@ -471,6 +442,18 @@
   </si>
   <si>
     <t>O sistema deve estar disponível para acesso online na maior parte do tempo (alta disponibilidade).</t>
+  </si>
+  <si>
+    <t>O sistema deve listar automaticamente na tela inicial todos os eventos cadastrados informando data e horario do evento.</t>
+  </si>
+  <si>
+    <t>O sistema deve apresentar mais detalhes dos eventos ao clicar neles.</t>
+  </si>
+  <si>
+    <t>RF32</t>
+  </si>
+  <si>
+    <t>O sistema deve apresentar, na área administrativa, uma interface de listagem para gerenciamento de todos os eventos cadastrados</t>
   </si>
 </sst>
 </file>
@@ -630,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -673,9 +656,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1051,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -1083,16 +1063,16 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="F2" s="27" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="F2" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:11" ht="31.5" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1105,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="21"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="10" t="s">
         <v>48</v>
       </c>
@@ -1128,7 +1108,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="21"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="2" t="s">
         <v>49</v>
       </c>
@@ -1151,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="21"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="2" t="s">
         <v>51</v>
       </c>
@@ -1174,12 +1154,12 @@
         <v>8</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="21"/>
+      <c r="E6" s="20"/>
       <c r="F6" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>8</v>
@@ -1197,12 +1177,12 @@
         <v>8</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="21"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>80</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>8</v>
@@ -1220,14 +1200,14 @@
         <v>18</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="21"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H8" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I8" s="8"/>
@@ -1243,12 +1223,12 @@
         <v>8</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="21"/>
+      <c r="E9" s="20"/>
       <c r="F9" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>8</v>
@@ -1266,13 +1246,13 @@
         <v>8</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="2" t="s">
@@ -1285,13 +1265,13 @@
         <v>18</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="2" t="s">
@@ -1304,322 +1284,329 @@
         <v>8</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-    </row>
-    <row r="15" spans="1:11" ht="45" customHeight="1">
+      <c r="E14" s="23"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
     </row>
     <row r="16" spans="1:11" ht="45" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1">
+      <c r="E16" s="20"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" ht="45" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="30" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="30" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-    </row>
-    <row r="21" spans="1:10" ht="45">
+      <c r="E20" s="20"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" ht="45">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-    </row>
-    <row r="22" spans="1:10" ht="30">
-      <c r="A22" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" ht="30">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C23" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-    </row>
-    <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="10" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" ht="30">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-    </row>
-    <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="11" t="s">
+      <c r="C24" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" ht="30">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-    </row>
-    <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="11" t="s">
+      <c r="C25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" ht="30">
+      <c r="A26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-    </row>
-    <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="14" t="s">
+      <c r="C26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" ht="30">
+      <c r="A27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-    </row>
-    <row r="27" spans="1:10" ht="30">
-      <c r="A27" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="8"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" ht="30">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:10" ht="30">
-      <c r="A28" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="11" t="s">
+      <c r="C28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="30">
+      <c r="A29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" ht="30">
-      <c r="A29" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="C29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="30">
+      <c r="A30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="12"/>
-    </row>
-    <row r="30" spans="1:10" ht="30">
-      <c r="A30" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="C30" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>69</v>
+        <v>8</v>
+      </c>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:10" ht="30">
+      <c r="A31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>68</v>
@@ -1627,11 +1614,11 @@
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:10" ht="30">
-      <c r="A32" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>70</v>
+      <c r="A32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>68</v>
@@ -1639,52 +1626,67 @@
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" ht="30">
-      <c r="A33" s="16" t="s">
-        <v>76</v>
+      <c r="A33" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>8</v>
+        <v>69</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="20"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="19"/>
+    <row r="34" spans="1:4" ht="30">
+      <c r="A34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="8"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="20"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="19"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="18"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
+      <c r="D36" s="18"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Requisitos Fun e NFun.xlsx
+++ b/Requisitos Fun e NFun.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="93">
   <si>
     <t>Código</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>RF08</t>
-  </si>
-  <si>
-    <t>O sistema deve atualizar visualmente os ícones conforme o banco de dados de cada parque, garantindo que apenas os serviços disponíveis sejam destacados.</t>
   </si>
   <si>
     <t>medio</t>
@@ -444,16 +441,37 @@
     <t>O sistema deve estar disponível para acesso online na maior parte do tempo (alta disponibilidade).</t>
   </si>
   <si>
-    <t>O sistema deve listar automaticamente na tela inicial todos os eventos cadastrados informando data e horario do evento.</t>
-  </si>
-  <si>
-    <t>O sistema deve apresentar mais detalhes dos eventos ao clicar neles.</t>
+    <t>O sistema deve apresentar, na área administrativa, uma interface de listagem para gerenciamento de todos os eventos cadastrados</t>
+  </si>
+  <si>
+    <t>Tela Inicial</t>
+  </si>
+  <si>
+    <t>Atividades</t>
+  </si>
+  <si>
+    <t>telas</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>cadastro de eventos</t>
+  </si>
+  <si>
+    <t>tele Inicial</t>
+  </si>
+  <si>
+    <t>O sistema deve listar, na tela inicial, todos os eventos cadastrados, exibindo obrigatoriamente: nome do evento, parque de realização e data.</t>
+  </si>
+  <si>
+    <t>O sistema deve permitir a visualização detalhada de um evento selecionado, exibindo: data de início, data de término, horário, e uma descrição completa</t>
+  </si>
+  <si>
+    <t>O sistema deve fornecer uma ferramenta de busca/filtro que permita ao usuário filtrar os eventos por parque ou visualizar a listagem completa.</t>
   </si>
   <si>
     <t>RF32</t>
-  </si>
-  <si>
-    <t>O sistema deve apresentar, na área administrativa, uma interface de listagem para gerenciamento de todos os eventos cadastrados</t>
   </si>
 </sst>
 </file>
@@ -523,7 +541,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -560,8 +578,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -608,12 +644,62 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -673,13 +759,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1037,20 +1142,24 @@
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
     <col min="2" max="2" width="90.5703125" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
     <col min="7" max="7" width="90.42578125" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>85</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>0</v>
@@ -1063,34 +1172,37 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
-      <c r="A2" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="A2" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="28"/>
+      <c r="F2" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A3" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="1:11" ht="31.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="10" t="s">
-        <v>48</v>
-      </c>
       <c r="G3" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>8</v>
@@ -1098,7 +1210,7 @@
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:11" ht="47.25" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="26" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1107,13 +1219,15 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -1121,7 +1235,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1130,13 +1244,15 @@
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="20"/>
+      <c r="D5" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -1144,7 +1260,7 @@
       <c r="I5" s="13"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1153,21 +1269,23 @@
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="20"/>
+      <c r="D6" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>76</v>
-      </c>
       <c r="H6" s="10" t="s">
         <v>8</v>
       </c>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1176,77 +1294,85 @@
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="20"/>
+      <c r="D7" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1">
+      <c r="A8" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G8" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="H8" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1">
+      <c r="A9" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="10" t="s">
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="H9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1">
+      <c r="A10" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="20"/>
+      <c r="D10" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="1"/>
       <c r="F10" s="22"/>
       <c r="G10" s="20"/>
       <c r="H10" s="22"/>
@@ -1255,17 +1381,19 @@
       <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>21</v>
+      <c r="A11" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="22"/>
       <c r="G11" s="20"/>
       <c r="H11" s="22"/>
@@ -1274,17 +1402,19 @@
       <c r="K11" s="18"/>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
+      <c r="A12" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="20"/>
+      <c r="D12" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="23"/>
       <c r="F12" s="22"/>
       <c r="G12" s="20"/>
       <c r="H12" s="22"/>
@@ -1293,17 +1423,19 @@
       <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="20"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="22"/>
       <c r="G13" s="20"/>
       <c r="H13" s="22"/>
@@ -1312,17 +1444,19 @@
       <c r="K13" s="18"/>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>84</v>
+      <c r="A14" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="23"/>
+      <c r="D14" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="1"/>
       <c r="F14" s="22"/>
       <c r="G14" s="20"/>
       <c r="H14" s="22"/>
@@ -1331,17 +1465,19 @@
       <c r="K14" s="18"/>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
+      <c r="A15" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="20"/>
+      <c r="D15" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="1"/>
       <c r="F15" s="22"/>
       <c r="G15" s="20"/>
       <c r="H15" s="22"/>
@@ -1349,54 +1485,61 @@
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
     </row>
-    <row r="16" spans="1:11" ht="45" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>29</v>
+    <row r="16" spans="1:11" ht="30" customHeight="1">
+      <c r="A16" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="20"/>
+      <c r="D16" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="1"/>
       <c r="F16" s="22"/>
       <c r="G16" s="20"/>
       <c r="H16" s="22"/>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
     </row>
     <row r="17" spans="1:10" ht="45" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>31</v>
+      <c r="A17" s="26" t="s">
+        <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="20"/>
+      <c r="D17" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="1"/>
       <c r="F17" s="22"/>
       <c r="G17" s="20"/>
       <c r="H17" s="22"/>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>33</v>
+    <row r="18" spans="1:10" ht="45" customHeight="1">
+      <c r="A18" s="26" t="s">
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="20"/>
+      <c r="D18" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="1"/>
       <c r="F18" s="22"/>
       <c r="G18" s="20"/>
       <c r="H18" s="22"/>
@@ -1404,17 +1547,19 @@
       <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="30" customHeight="1">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
+      <c r="A19" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="20"/>
+      <c r="D19" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="1"/>
       <c r="F19" s="22"/>
       <c r="G19" s="20"/>
       <c r="H19" s="22"/>
@@ -1422,17 +1567,19 @@
       <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="30" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>36</v>
+      <c r="A20" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="20"/>
+      <c r="D20" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="1"/>
       <c r="F20" s="22"/>
       <c r="G20" s="20"/>
       <c r="H20" s="22"/>
@@ -1440,35 +1587,39 @@
       <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="30" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>40</v>
+      <c r="A21" s="26" t="s">
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="20"/>
+        <v>37</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="1"/>
       <c r="F21" s="22"/>
       <c r="G21" s="20"/>
       <c r="H21" s="22"/>
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" ht="45">
-      <c r="A22" s="2" t="s">
-        <v>41</v>
+    <row r="22" spans="1:10" ht="30" customHeight="1">
+      <c r="A22" s="26" t="s">
+        <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="20"/>
+      <c r="D22" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="1"/>
       <c r="F22" s="22"/>
       <c r="G22" s="20"/>
       <c r="H22" s="22"/>
@@ -1476,17 +1627,19 @@
       <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="2" t="s">
-        <v>42</v>
+      <c r="A23" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="20"/>
+        <v>37</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="8"/>
       <c r="F23" s="22"/>
       <c r="G23" s="20"/>
       <c r="H23" s="22"/>
@@ -1494,17 +1647,19 @@
       <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="2" t="s">
-        <v>45</v>
+      <c r="A24" s="26" t="s">
+        <v>44</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="20"/>
+      <c r="D24" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="8"/>
       <c r="F24" s="22"/>
       <c r="G24" s="20"/>
       <c r="H24" s="22"/>
@@ -1512,17 +1667,19 @@
       <c r="J24" s="18"/>
     </row>
     <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="2" t="s">
-        <v>46</v>
+      <c r="A25" s="26" t="s">
+        <v>45</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="20"/>
+      <c r="D25" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="8"/>
       <c r="F25" s="22"/>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -1530,162 +1687,192 @@
       <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="2" t="s">
-        <v>60</v>
+      <c r="A26" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
+      <c r="D26" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="22"/>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="1:10" ht="30">
-      <c r="A27" s="2" t="s">
-        <v>61</v>
+    <row r="27" spans="1:10" ht="45">
+      <c r="A27" s="26" t="s">
+        <v>60</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="18"/>
+        <v>37</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="8"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="1:10" ht="30">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:10" ht="45">
+      <c r="A28" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="C28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="45">
+      <c r="A29" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="45">
+      <c r="A30" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:10" ht="30">
-      <c r="A29" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:10" ht="30">
-      <c r="A30" s="2" t="s">
+      <c r="C30" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="12"/>
+    </row>
+    <row r="31" spans="1:10" ht="45">
+      <c r="A31" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="12"/>
-    </row>
-    <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="2" t="s">
+      <c r="D31" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="45">
+      <c r="A32" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="1:5" ht="45">
+      <c r="A33" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="B33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="30">
-      <c r="A32" s="2" t="s">
+      <c r="C33" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="1:5" ht="45">
+      <c r="A34" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="8"/>
-    </row>
-    <row r="33" spans="1:4" ht="30">
-      <c r="A33" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="8"/>
-    </row>
-    <row r="34" spans="1:4" ht="30">
-      <c r="A34" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="C34" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="D34" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" s="8"/>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="16"/>
       <c r="B35" s="20"/>
       <c r="C35" s="19"/>
       <c r="D35" s="18"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" s="19"/>
       <c r="B36" s="20"/>
       <c r="C36" s="19"/>
       <c r="D36" s="18"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:5">
       <c r="A38" s="18"/>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="18"/>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:5">
       <c r="A40" s="18"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" s="18"/>
     </row>
   </sheetData>

--- a/Requisitos Fun e NFun.xlsx
+++ b/Requisitos Fun e NFun.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="91">
   <si>
     <t>Código</t>
   </si>
@@ -329,21 +329,6 @@
     <t xml:space="preserve">O sistema deve disponibilizar um formulário para inclusão de eventos com os campos Nome, Datas (Início/Término), Horários (Início/Término), Local e Descrição, além de um botão "Salvar Evento". </t>
   </si>
   <si>
-    <r>
-      <t>Consistência Cronológica:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> O sistema deve validar se a Data e Horário de Término são posteriores à Data e Horário de Início, exibindo um alerta de erro caso a cronologia seja inválida.</t>
-    </r>
-  </si>
-  <si>
     <t>RF27</t>
   </si>
   <si>
@@ -470,15 +455,12 @@
   <si>
     <t>O sistema deve fornecer uma ferramenta de busca/filtro que permita ao usuário filtrar os eventos por parque ou visualizar a listagem completa.</t>
   </si>
-  <si>
-    <t>RF32</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,8 +522,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,12 +563,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -699,7 +682,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -732,7 +715,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -759,9 +741,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -774,17 +753,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -792,6 +771,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1136,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -1149,17 +1131,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>85</v>
+      <c r="D1" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>0</v>
@@ -1172,30 +1154,30 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="28"/>
-      <c r="F2" s="33" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="26"/>
+      <c r="F2" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="1:11" ht="31.5" customHeight="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>83</v>
+      <c r="C3" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="10" t="s">
@@ -1210,7 +1192,7 @@
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:11" ht="47.25" customHeight="1">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1219,8 +1201,8 @@
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="30" t="s">
-        <v>83</v>
+      <c r="D4" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="2" t="s">
@@ -1235,7 +1217,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1244,8 +1226,8 @@
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>83</v>
+      <c r="D5" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="2" t="s">
@@ -1257,10 +1239,10 @@
       <c r="H5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="13"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="24" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1269,23 +1251,23 @@
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>83</v>
+      <c r="D6" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="17" t="s">
-        <v>75</v>
-      </c>
       <c r="H6" s="10" t="s">
         <v>8</v>
       </c>
       <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="24" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1294,23 +1276,23 @@
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="30" t="s">
-        <v>83</v>
+      <c r="D7" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>79</v>
+        <v>75</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="12"/>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="24" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1319,23 +1301,23 @@
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="30" t="s">
-        <v>83</v>
+      <c r="D8" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="H8" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="20" t="s">
         <v>8</v>
       </c>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1344,15 +1326,15 @@
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="30" t="s">
-        <v>83</v>
+      <c r="D9" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>8</v>
@@ -1360,7 +1342,7 @@
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="24" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1369,19 +1351,19 @@
       <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>83</v>
+      <c r="D10" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="24" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1390,82 +1372,82 @@
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="30" t="s">
-        <v>83</v>
+      <c r="D11" s="28" t="s">
+        <v>82</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="33"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:11" ht="30" customHeight="1">
+      <c r="A13" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="1:11" ht="30" customHeight="1">
-      <c r="A13" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="17" t="s">
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1">
+      <c r="A14" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" spans="1:11" ht="30" customHeight="1">
-      <c r="A14" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>91</v>
-      </c>
       <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>88</v>
+      <c r="D14" s="28" t="s">
+        <v>87</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="24" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1474,19 +1456,19 @@
       <c r="C15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="29" t="s">
-        <v>84</v>
+      <c r="D15" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="24" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1495,19 +1477,19 @@
       <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>84</v>
+      <c r="D16" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="45" customHeight="1">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="24" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1516,18 +1498,18 @@
       <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="29" t="s">
-        <v>84</v>
+      <c r="D17" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
     </row>
     <row r="18" spans="1:10" ht="45" customHeight="1">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="24" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1536,18 +1518,18 @@
       <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="29" t="s">
-        <v>84</v>
+      <c r="D18" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" ht="30" customHeight="1">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="24" t="s">
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1556,18 +1538,18 @@
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="29" t="s">
-        <v>84</v>
+      <c r="D19" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" ht="30" customHeight="1">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -1576,18 +1558,18 @@
       <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="29" t="s">
-        <v>84</v>
+      <c r="D20" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E20" s="1"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" ht="30" customHeight="1">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="24" t="s">
         <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1596,18 +1578,18 @@
       <c r="C21" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>84</v>
+      <c r="D21" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
     </row>
     <row r="22" spans="1:10" ht="30" customHeight="1">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="24" t="s">
         <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1616,18 +1598,18 @@
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="29" t="s">
-        <v>84</v>
+      <c r="D22" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
     </row>
     <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="24" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1636,18 +1618,18 @@
       <c r="C23" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="30" t="s">
-        <v>86</v>
+      <c r="D23" s="28" t="s">
+        <v>85</v>
       </c>
       <c r="E23" s="8"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="24" t="s">
         <v>44</v>
       </c>
       <c r="B24" s="10" t="s">
@@ -1656,18 +1638,18 @@
       <c r="C24" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>86</v>
+      <c r="D24" s="28" t="s">
+        <v>85</v>
       </c>
       <c r="E24" s="8"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="24" t="s">
         <v>45</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -1676,18 +1658,18 @@
       <c r="C25" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>86</v>
+      <c r="D25" s="28" t="s">
+        <v>85</v>
       </c>
       <c r="E25" s="8"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
     </row>
     <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -1696,38 +1678,38 @@
       <c r="C26" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="30" t="s">
-        <v>86</v>
+      <c r="D26" s="28" t="s">
+        <v>85</v>
       </c>
       <c r="E26" s="8"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" ht="45">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="30" t="s">
-        <v>87</v>
+      <c r="D27" s="28" t="s">
+        <v>86</v>
       </c>
       <c r="E27" s="8"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" spans="1:10" ht="45">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="24" t="s">
         <v>62</v>
       </c>
       <c r="B28" s="10" t="s">
@@ -1736,19 +1718,19 @@
       <c r="C28" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="30" t="s">
-        <v>87</v>
+      <c r="D28" s="28" t="s">
+        <v>86</v>
       </c>
       <c r="E28" s="8"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:10" ht="45">
-      <c r="A29" s="26" t="s">
-        <v>65</v>
+      <c r="A29" s="24" t="s">
+        <v>64</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>61</v>
@@ -1756,124 +1738,109 @@
       <c r="C29" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="30" t="s">
-        <v>87</v>
+      <c r="D29" s="28" t="s">
+        <v>86</v>
       </c>
       <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:10" ht="45">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="12"/>
+      <c r="D30" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" spans="1:10" ht="45">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="45">
+      <c r="A32" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="1:5" ht="45">
+      <c r="A33" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" spans="1:10" ht="45">
-      <c r="A32" s="26" t="s">
+      <c r="B33" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="1:5" ht="45">
-      <c r="A33" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="C33" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>87</v>
+        <v>8</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>86</v>
       </c>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" ht="45">
-      <c r="A34" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="8"/>
+    <row r="34" spans="1:5">
+      <c r="A34" s="15"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="17"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="16"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="18"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="19"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="18"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="18"/>
+      <c r="A40" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
